--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487908_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487908_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. LLAMAS PRADO</t>
+          <t>D. HAYMAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0801</v>
+        <v>5.5052</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9648</v>
+        <v>5.2064</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1153</v>
+        <v>0.2988</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9583</v>
+        <v>2.9456</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4627</v>
+        <v>3.3538</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4956</v>
+        <v>-0.4082</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8686</v>
+        <v>4.5052</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3771</v>
+        <v>4.5624</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4915</v>
+        <v>-0.0572</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0897</v>
+        <v>-1.5596</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0856</v>
+        <v>-1.2086</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0041</v>
+        <v>-0.351</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0406</v>
+        <v>2.7055</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1487</v>
+        <v>-0.6266</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1338</v>
+        <v>-0.0095</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.015</v>
+        <v>-0.6171</v>
       </c>
       <c r="V2" t="n">
-        <v>0.23</v>
+        <v>1.5213</v>
       </c>
       <c r="W2" t="n">
-        <v>0.23</v>
+        <v>1.7513</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. DENG</t>
+          <t>J. LLAMAS PRADO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7686</v>
+        <v>4.6939</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0329</v>
+        <v>3.6666</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2643</v>
+        <v>1.0272</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7322</v>
+        <v>3.9583</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6162</v>
+        <v>3.4627</v>
       </c>
       <c r="I3" t="n">
-        <v>1.116</v>
+        <v>0.4956</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5487</v>
+        <v>3.8686</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7225</v>
+        <v>3.3771</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8262</v>
+        <v>0.4915</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1835</v>
+        <v>0.0897</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1063</v>
+        <v>0.0856</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2898</v>
+        <v>0.0041</v>
       </c>
       <c r="P3" t="n">
         <v>1.0406</v>
@@ -688,28 +688,28 @@
         <v>1.0406</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6505</v>
+        <v>-0.535</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3295</v>
+        <v>-0.4319</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3209</v>
+        <v>-0.103</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3538</v>
+        <v>0.23</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8137</v>
+        <v>0.23</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. HAYMAN</t>
+          <t>M. DENG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5263</v>
+        <v>4.6363</v>
       </c>
       <c r="E4" t="n">
-        <v>4.433</v>
+        <v>4.8419</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09329999999999999</v>
+        <v>-0.2056</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9456</v>
+        <v>4.7322</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3538</v>
+        <v>3.6162</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4082</v>
+        <v>1.116</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5052</v>
+        <v>4.5487</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5624</v>
+        <v>3.7225</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0572</v>
+        <v>0.8262</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5596</v>
+        <v>0.1835</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2086</v>
+        <v>-0.1063</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.351</v>
+        <v>0.2898</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7055</v>
+        <v>1.0406</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6056</v>
+        <v>-0.7827</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7829</v>
+        <v>-0.5205</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8226</v>
+        <v>-0.2622</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5213</v>
+        <v>-0.3538</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7513</v>
+        <v>0.8137</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. LLAMAS MARTINEZ</t>
+          <t>D. CEBOLLA PORCAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.75</v>
+        <v>1.7151</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7691</v>
+        <v>0.2105</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0192</v>
+        <v>1.5046</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7929</v>
+        <v>1.1286</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7889</v>
+        <v>3.3966</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.996</v>
+        <v>-2.268</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5115</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2258</v>
+        <v>3.3151</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7144</v>
+        <v>-2.7007</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7186</v>
+        <v>0.5141</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4369</v>
+        <v>0.0814</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2817</v>
+        <v>0.4327</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0835</v>
+        <v>-1.3084</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2577</v>
+        <v>-0.6338</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3412</v>
+        <v>-0.6745</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. CEBOLLA PORCAR</t>
+          <t>R. LLAMAS MARTINEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9756</v>
+        <v>1.3404</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2648</v>
+        <v>1.4477</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2403</v>
+        <v>-0.1072</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1286</v>
+        <v>0.7929</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3966</v>
+        <v>1.7889</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.268</v>
+        <v>-0.996</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6143999999999999</v>
+        <v>1.5115</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3151</v>
+        <v>2.2258</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.7007</v>
+        <v>-0.7144</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5141</v>
+        <v>-0.7186</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0814</v>
+        <v>-0.4369</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4327</v>
+        <v>-0.2817</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.0479</v>
+        <v>-0.493</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1091</v>
+        <v>-0.0638</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9388</v>
+        <v>-0.4292</v>
       </c>
       <c r="V6" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4014</v>
+        <v>1.042</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3618</v>
+        <v>1.8557</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9605</v>
+        <v>-0.8137</v>
       </c>
       <c r="G7" t="n">
         <v>1.009</v>
@@ -1000,13 +1000,13 @@
         <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1508</v>
+        <v>-0.5102</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7177</v>
+        <v>-0.2238</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4332</v>
+        <v>-0.2864</v>
       </c>
       <c r="V7" t="n">
         <v>1.1675</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2466</v>
+        <v>0.2809</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0983</v>
+        <v>-1.6883</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8517</v>
+        <v>1.9691</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0049</v>
@@ -1078,13 +1078,13 @@
         <v>1.2487</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2604</v>
+        <v>-0.733</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.1771</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6732</v>
+        <v>-0.5558</v>
       </c>
       <c r="V8" t="n">
         <v>-0.23</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4385</v>
+        <v>-0.4437</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.334</v>
+        <v>0.1599</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1045</v>
+        <v>-0.6036</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8328</v>
@@ -1156,13 +1156,13 @@
         <v>2.0812</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0032</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9134</v>
+        <v>-0.4195</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9102</v>
+        <v>0.4111</v>
       </c>
       <c r="V9" t="n">
         <v>1.3975</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1742</v>
+        <v>-1.5544</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.587</v>
+        <v>-1.9085</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4128</v>
+        <v>0.3541</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3734</v>
@@ -1234,13 +1234,13 @@
         <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2597</v>
+        <v>-0.6398</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0619</v>
+        <v>-0.2595</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3216</v>
+        <v>-0.3803</v>
       </c>
       <c r="V10" t="n">
         <v>0.7076</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. AMADASUN</t>
+          <t>D. BULTO CASTILLO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9422</v>
+        <v>-2.5628</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9253</v>
+        <v>-1.5086</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.8675</v>
+        <v>-1.0542</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1017</v>
+        <v>-1.6391</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7784</v>
+        <v>-0.9337</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3233</v>
+        <v>-0.7054</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0907</v>
+        <v>-0.4633</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3853</v>
+        <v>0.1727</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7054</v>
+        <v>-0.636</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1924</v>
+        <v>-1.1758</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1637</v>
+        <v>-1.1064</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0287</v>
+        <v>-0.0694</v>
       </c>
       <c r="P11" t="n">
         <v>0.2081</v>
@@ -1312,28 +1312,28 @@
         <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2349</v>
+        <v>0.0357</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1239</v>
+        <v>-0.0047</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3588</v>
+        <v>0.0405</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8137</v>
+        <v>-1.1675</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7513</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.565</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. BULTO CASTILLO</t>
+          <t>M. AMADASUN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,40 +1345,40 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9495</v>
+        <v>-2.5972</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8954</v>
+        <v>1.329</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0542</v>
+        <v>-3.9262</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.6391</v>
+        <v>-1.1017</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9337</v>
+        <v>-0.7784</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7054</v>
+        <v>-0.3233</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4633</v>
+        <v>1.0907</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1727</v>
+        <v>0.3853</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.636</v>
+        <v>0.7054</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1758</v>
+        <v>-2.1924</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1064</v>
+        <v>-1.1637</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0694</v>
+        <v>-1.0287</v>
       </c>
       <c r="P12" t="n">
         <v>0.2081</v>
@@ -1390,22 +1390,22 @@
         <v>1.2487</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.351</v>
+        <v>-0.8899</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3915</v>
+        <v>-0.4724</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0405</v>
+        <v>-0.4175</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1675</v>
+        <v>-0.8137</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1675</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="13">
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.751</v>
+        <v>12.0557</v>
       </c>
       <c r="E13" t="n">
-        <v>12.3074</v>
+        <v>13.6123</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.556800000000001</v>
+        <v>-1.556700000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>9.614699999999999</v>
+        <v>9.614700000000001</v>
       </c>
       <c r="H13" t="n">
         <v>12.4516</v>
@@ -1447,13 +1447,13 @@
         <v>18.7809</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3878999999999998</v>
+        <v>-0.3878999999999997</v>
       </c>
       <c r="M13" t="n">
         <v>-8.778600000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.329299999999999</v>
+        <v>-6.3293</v>
       </c>
       <c r="O13" t="n">
         <v>-2.4493</v>
@@ -1468,13 +1468,13 @@
         <v>15.6088</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.796199999999999</v>
+        <v>-6.4914</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.5216</v>
+        <v>-3.2165</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.2746</v>
+        <v>-3.2744</v>
       </c>
       <c r="V13" t="n">
         <v>2.688900000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. BADJI</t>
+          <t>M. NIANG NDONGO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1594</v>
+        <v>4.5</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3653</v>
+        <v>5.4645</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7942</v>
+        <v>-0.9645</v>
       </c>
       <c r="G14" t="n">
-        <v>3.3105</v>
+        <v>3.3358</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2875</v>
+        <v>0.0301</v>
       </c>
       <c r="I14" t="n">
-        <v>1.023</v>
+        <v>3.3057</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2536</v>
+        <v>5.6508</v>
       </c>
       <c r="K14" t="n">
-        <v>3.0185</v>
+        <v>2.7779</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2351</v>
+        <v>2.873</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0569</v>
+        <v>-2.3151</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.731</v>
+        <v>-2.7478</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7879</v>
+        <v>0.4327</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6244</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2487</v>
+        <v>-1.6649</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="S14" t="n">
-        <v>4.287</v>
+        <v>1.1205</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3603</v>
+        <v>0.5587</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9267</v>
+        <v>0.5618</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8137</v>
+        <v>0.4599</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8137</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. NIANG NDONGO</t>
+          <t>P. BADJI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9961</v>
+        <v>4.0911</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1074</v>
+        <v>2.9722</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1113</v>
+        <v>1.1189</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3358</v>
+        <v>3.3105</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0301</v>
+        <v>2.2875</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3057</v>
+        <v>1.023</v>
       </c>
       <c r="J15" t="n">
-        <v>5.6508</v>
+        <v>3.2536</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7779</v>
+        <v>3.0185</v>
       </c>
       <c r="L15" t="n">
-        <v>2.873</v>
+        <v>0.2351</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.3151</v>
+        <v>0.0569</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.7478</v>
+        <v>-0.731</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4327</v>
+        <v>0.7879</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4162</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.6649</v>
+        <v>-1.2487</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6166</v>
+        <v>2.2187</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2016</v>
+        <v>0.9673</v>
       </c>
       <c r="U15" t="n">
-        <v>0.415</v>
+        <v>1.2514</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4599</v>
+        <v>-0.8137</v>
       </c>
       <c r="W15" t="n">
-        <v>0.9199000000000001</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4599</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6053</v>
+        <v>2.2967</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8156</v>
+        <v>2.5657</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2104</v>
+        <v>-0.2691</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4359</v>
@@ -1702,13 +1702,13 @@
         <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1442</v>
+        <v>0.8356</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5376</v>
+        <v>0.2125</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6818</v>
+        <v>0.6231</v>
       </c>
       <c r="V16" t="n">
         <v>2.1051</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2811</v>
+        <v>-0.2517</v>
       </c>
       <c r="E17" t="n">
         <v>-0.0461</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.235</v>
+        <v>-0.2057</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8626</v>
@@ -1780,13 +1780,13 @@
         <v>0.2081</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2277</v>
+        <v>0.2571</v>
       </c>
       <c r="T17" t="n">
         <v>0.1429</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0848</v>
+        <v>0.1142</v>
       </c>
       <c r="V17" t="n">
         <v>0.3538</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9146</v>
+        <v>-0.6915</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2555</v>
+        <v>0.1731</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6591</v>
+        <v>-0.8646</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3256</v>
@@ -1858,13 +1858,13 @@
         <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1116</v>
+        <v>0.3347</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1833</v>
+        <v>0.2453</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2949</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1168</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>O. ARDANZA BERNAOLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1658</v>
+        <v>-0.7127</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2734</v>
+        <v>-0.4523</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8924</v>
+        <v>-0.2604</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7756</v>
+        <v>-0.3475</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3838</v>
+        <v>-0.7141</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3919</v>
+        <v>0.3666</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.6364</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.0576</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.5788</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7756</v>
+        <v>-0.9839</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3838</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3919</v>
+        <v>-0.2123</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2081</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2081</v>
+        <v>-1.2487</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.146</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.216</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1168</v>
+        <v>0.1132</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X19" t="n">
         <v>-0.1168</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. ARDANZA BERNAOLA</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2103</v>
+        <v>-0.9514</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7738</v>
+        <v>-0.059</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4365</v>
+        <v>-0.8924</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3475</v>
+        <v>-0.7756</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7141</v>
+        <v>-0.3838</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3666</v>
+        <v>-0.3919</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6364</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0576</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5788</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9839</v>
+        <v>-0.7756</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.3838</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2123</v>
+        <v>-0.3919</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6244</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.2487</v>
+        <v>-0.2081</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6244</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3517</v>
+        <v>0.1491</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3915</v>
+        <v>0.1491</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0398</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1132</v>
+        <v>-0.1168</v>
       </c>
       <c r="W20" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>-0.1168</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.543</v>
+        <v>-3.5347</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8619</v>
+        <v>-3.3075</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4049</v>
+        <v>-0.2272</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.2165</v>
+        <v>-1.9001</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.5201</v>
+        <v>-2.8635</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6964</v>
+        <v>0.9634</v>
       </c>
       <c r="J21" t="n">
-        <v>0.421</v>
+        <v>-1.2059</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2642</v>
+        <v>-1.2752</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1568</v>
+        <v>0.0694</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.6375</v>
+        <v>-0.6942</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.7844</v>
+        <v>-1.5882</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8532</v>
+        <v>0.894</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4162</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.6649</v>
+        <v>-2.4974</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>1.9141</v>
+        <v>0.844</v>
       </c>
       <c r="T21" t="n">
-        <v>1.646</v>
+        <v>0.3958</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2682</v>
+        <v>0.4482</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8244</v>
+        <v>-0.8137</v>
       </c>
       <c r="W21" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2843</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0617</v>
+        <v>-3.6924</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6289</v>
+        <v>-0.3168</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4328</v>
+        <v>-3.3756</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9001</v>
+        <v>-3.2165</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.8635</v>
+        <v>-2.5201</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9634</v>
+        <v>-0.6964</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2059</v>
+        <v>0.421</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2752</v>
+        <v>0.2642</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0694</v>
+        <v>0.1568</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6942</v>
+        <v>-3.6375</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5882</v>
+        <v>-2.7844</v>
       </c>
       <c r="O22" t="n">
-        <v>0.894</v>
+        <v>-0.8532</v>
       </c>
       <c r="P22" t="n">
+        <v>-0.4162</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-1.6649</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-2.4974</v>
-      </c>
       <c r="R22" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3171</v>
+        <v>0.7648</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0743</v>
+        <v>0.4672</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2427</v>
+        <v>0.2975</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8137</v>
+        <v>-0.8244</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8137</v>
+        <v>-1.2843</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6187</v>
+        <v>-4.9067</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4109</v>
+        <v>-3.8752</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2077</v>
+        <v>-1.0316</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7979</v>
@@ -2248,13 +2248,13 @@
         <v>1.8731</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2198</v>
+        <v>0.9318</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.28</v>
+        <v>0.2558</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4998</v>
+        <v>0.676</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1675</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.7164</v>
+        <v>-6.8974</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2049</v>
+        <v>-1.562</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.5115</v>
+        <v>-5.3354</v>
       </c>
       <c r="G24" t="n">
         <v>-4.599</v>
@@ -2326,13 +2326,13 @@
         <v>0.8325</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.625</v>
+        <v>0.1941</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6929</v>
+        <v>-0.05</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0679</v>
+        <v>0.244</v>
       </c>
       <c r="V24" t="n">
         <v>-1.868</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.7508</v>
+        <v>-10.7507</v>
       </c>
       <c r="E25" t="n">
-        <v>1.556700000000002</v>
+        <v>1.556600000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-12.3074</v>
+        <v>-12.3076</v>
       </c>
       <c r="G25" t="n">
         <v>-9.6144</v>
@@ -2377,7 +2377,7 @@
         <v>2.8371</v>
       </c>
       <c r="J25" t="n">
-        <v>8.778500000000003</v>
+        <v>8.778500000000001</v>
       </c>
       <c r="K25" t="n">
         <v>6.3296</v>
@@ -2395,16 +2395,16 @@
         <v>0.3878000000000004</v>
       </c>
       <c r="P25" t="n">
-        <v>-6.2436</v>
+        <v>-6.243599999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-15.6086</v>
       </c>
       <c r="R25" t="n">
-        <v>9.365500000000001</v>
+        <v>9.365499999999997</v>
       </c>
       <c r="S25" t="n">
-        <v>7.796199999999999</v>
+        <v>7.796399999999999</v>
       </c>
       <c r="T25" t="n">
         <v>3.2746</v>
